--- a/InputFiles/ICDC/TC44_ICDC_COTC021_Breed-Rottweiler.xlsx
+++ b/InputFiles/ICDC/TC44_ICDC_COTC021_Breed-Rottweiler.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\epishinavv\git\Commons_Automation\InputFiles\ICDC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/epishinavv/git/Commons_Automation/InputFiles/ICDC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50FDBAD7-8FEC-43F9-BE3E-12FA6EA29562}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B25F95AD-29F7-2149-9637-ED7C66847998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
+    <workbookView xWindow="30240" yWindow="600" windowWidth="29040" windowHeight="15720" xr2:uid="{8362173B-D28C-47E7-8626-98E16101E601}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -270,6 +270,7 @@
         WHEN cf.file_name LIKE '%.xlsx' THEN 'xlsx'
         WHEN cf.file_name LIKE '%.h5' THEN 'h5'
         WHEN cf.file_name LIKE '%.tsv' THEN 'tsv'
+        WHEN cf.file_name LIKE '%.RCC' THEN 'RCC'
         ELSE 'Unknown'
     END AS "Format",
     cf.file_type AS "File Type",
@@ -336,9 +337,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -391,11 +399,14 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -720,15 +731,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C538400-E87C-4027-A918-A51DB80B3430}">
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="75.77734375" customWidth="1"/>
-    <col min="4" max="4" width="70.109375" customWidth="1"/>
-    <col min="5" max="5" width="63.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="75.83203125" customWidth="1"/>
+    <col min="4" max="4" width="70.1640625" customWidth="1"/>
+    <col min="5" max="5" width="63.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -745,7 +756,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -762,7 +773,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -771,16 +782,16 @@
       </c>
       <c r="C3" s="2"/>
     </row>
-    <row r="4" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="2"/>
     </row>
-    <row r="5" spans="1:5" ht="409.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -789,11 +800,11 @@
       </c>
       <c r="C5" s="1"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="C6" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="4" type="noConversion"/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
